--- a/admin/DSinPython예산.xlsx
+++ b/admin/DSinPython예산.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DSpy\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21924" windowHeight="9084"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21924" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="예산" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>세목</t>
   </si>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>집행합계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -320,6 +324,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -328,9 +335,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -888,7 +892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A4:E20"/>
+  <dimension ref="A4:I20"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.796875" customWidth="1"/>
@@ -897,8 +901,8 @@
     <col min="4" max="4" width="34.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -914,8 +918,11 @@
       <c r="E5" s="11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -929,7 +936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -945,9 +952,13 @@
       <c r="E7">
         <v>485190</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="12" t="s">
+      <c r="I7">
+        <f t="shared" ref="I7:I10" si="0">SUM(E7:H7)</f>
+        <v>485190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -960,9 +971,13 @@
       <c r="E8">
         <v>80300</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="13"/>
+      <c r="I8">
+        <f t="shared" si="0"/>
+        <v>80300</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
@@ -970,9 +985,13 @@
         <v>13</v>
       </c>
       <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="13"/>
+      <c r="I9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="14"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
@@ -983,9 +1002,13 @@
       <c r="E10">
         <v>101700</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="14"/>
+      <c r="I10">
+        <f t="shared" si="0"/>
+        <v>101700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="15"/>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
@@ -996,14 +1019,25 @@
       <c r="E11">
         <v>37000</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11">
+        <v>48500</v>
+      </c>
+      <c r="I11">
+        <f>SUM(E11:H11)</f>
+        <v>85500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>33</v>
       </c>
       <c r="E12">
         <f>SUM(E6:E11)</f>
         <v>704190</v>
+      </c>
+      <c r="I12">
+        <f>SUM(I7:I11)</f>
+        <v>752690</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.4">
@@ -1215,7 +1249,7 @@
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="12">
         <v>44344</v>
       </c>
       <c r="C2">

--- a/admin/DSinPython예산.xlsx
+++ b/admin/DSinPython예산.xlsx
@@ -9,14 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21924" windowHeight="8160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21930" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="예산" sheetId="1" r:id="rId1"/>
-    <sheet name="도서구입" sheetId="4" r:id="rId2"/>
-    <sheet name="연구환경비" sheetId="2" r:id="rId3"/>
-    <sheet name="재료비" sheetId="3" r:id="rId4"/>
-    <sheet name="회의비" sheetId="5" r:id="rId5"/>
+    <sheet name="문구류" sheetId="6" r:id="rId2"/>
+    <sheet name="도서구입" sheetId="4" r:id="rId3"/>
+    <sheet name="연구환경비" sheetId="2" r:id="rId4"/>
+    <sheet name="재료비" sheetId="3" r:id="rId5"/>
+    <sheet name="회의비" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>세목</t>
   </si>
@@ -144,6 +145,26 @@
   </si>
   <si>
     <t>집행합계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>합계</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로마키</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>크로마키</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽걸이</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>연장가로봉</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -358,6 +379,53 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3073" name="AutoShape 1" descr="image.png"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="1257300"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>30479</xdr:rowOff>
@@ -472,7 +540,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -893,16 +961,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:I20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.796875" customWidth="1"/>
-    <col min="2" max="2" width="13.796875" customWidth="1"/>
-    <col min="3" max="3" width="10.59765625" customWidth="1"/>
-    <col min="4" max="4" width="34.69921875" customWidth="1"/>
+    <col min="1" max="1" width="11.75" customWidth="1"/>
+    <col min="2" max="2" width="13.75" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="34.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -922,7 +990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -936,7 +1004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -957,7 +1025,7 @@
         <v>485190</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
@@ -976,7 +1044,7 @@
         <v>80300</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -984,13 +1052,18 @@
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>73000</v>
+      </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+        <v>73000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1007,7 +1080,7 @@
         <v>101700</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="15"/>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1027,20 +1100,20 @@
         <v>85500</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>33</v>
       </c>
       <c r="E12">
         <f>SUM(E6:E11)</f>
-        <v>704190</v>
+        <v>777190</v>
       </c>
       <c r="I12">
         <f>SUM(I7:I11)</f>
-        <v>752690</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
+        <v>825690</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B20" s="5"/>
     </row>
   </sheetData>
@@ -1049,24 +1122,69 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:C6"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3">
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5">
+        <v>38000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6">
+        <f>SUM(C3:C5)</f>
+        <v>73000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="63.09765625" customWidth="1"/>
+    <col min="1" max="1" width="63.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1074,7 +1192,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1082,7 +1200,7 @@
         <v>54300</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1098,15 +1216,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:C6"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.69921875" customWidth="1"/>
+    <col min="1" max="1" width="39.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
@@ -1117,7 +1235,7 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
@@ -1128,7 +1246,7 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1139,7 +1257,7 @@
         <v>20500</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1150,83 +1268,13 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="7">
         <f>SUM(C2:C5)</f>
         <v>101700</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:C7"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="43.296875" customWidth="1"/>
-    <col min="3" max="3" width="9.69921875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="8">
-        <v>156790</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8">
-        <v>36400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" s="8">
-        <v>267600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" s="8">
-        <v>24400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="9">
-        <f>SUM(C3:C6)</f>
-        <v>485190</v>
       </c>
     </row>
   </sheetData>
@@ -1239,13 +1287,83 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A3:C7"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.25" customWidth="1"/>
+    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8">
+        <v>156790</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8">
+        <v>36400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" s="8">
+        <v>267600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>24400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="9">
+        <f>SUM(C3:C6)</f>
+        <v>485190</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:C2"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>32</v>
       </c>

--- a/admin/DSinPython예산.xlsx
+++ b/admin/DSinPython예산.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21930" windowHeight="8160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21936" windowHeight="8160"/>
   </bookViews>
   <sheets>
     <sheet name="예산" sheetId="1" r:id="rId1"/>
@@ -961,16 +961,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A4:I20"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
-    <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="4" max="4" width="34.75" customWidth="1"/>
+    <col min="1" max="1" width="11.69921875" customWidth="1"/>
+    <col min="2" max="2" width="13.69921875" customWidth="1"/>
+    <col min="3" max="3" width="10.59765625" customWidth="1"/>
+    <col min="4" max="4" width="34.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="5" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
@@ -990,7 +990,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>485190</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="13" t="s">
         <v>18</v>
       </c>
@@ -1044,7 +1044,7 @@
         <v>80300</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="14"/>
       <c r="B9" s="2" t="s">
         <v>14</v>
@@ -1058,12 +1058,15 @@
       <c r="E9">
         <v>73000</v>
       </c>
+      <c r="F9">
+        <v>62580</v>
+      </c>
       <c r="I9">
         <f t="shared" si="0"/>
-        <v>73000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>135580</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14"/>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1080,7 +1083,7 @@
         <v>101700</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="15"/>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1100,7 +1103,7 @@
         <v>85500</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>33</v>
       </c>
@@ -1110,10 +1113,10 @@
       </c>
       <c r="I12">
         <f>SUM(I7:I11)</f>
-        <v>825690</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+        <v>888270</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B20" s="5"/>
     </row>
   </sheetData>
@@ -1129,9 +1132,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:C6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -1139,7 +1142,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>38</v>
       </c>
@@ -1155,7 +1158,7 @@
         <v>38000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>39</v>
       </c>
@@ -1174,17 +1177,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="63.125" customWidth="1"/>
+    <col min="1" max="1" width="63.09765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>54300</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1219,12 +1222,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:C6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="39.75" customWidth="1"/>
+    <col min="1" max="1" width="39.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
         <v>19</v>
       </c>
@@ -1235,7 +1238,7 @@
         <v>34000</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="6" t="s">
         <v>20</v>
       </c>
@@ -1246,7 +1249,7 @@
         <v>19200</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1257,7 +1260,7 @@
         <v>20500</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -1268,7 +1271,7 @@
         <v>28000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
         <v>21</v>
       </c>
@@ -1288,13 +1291,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:C7"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="43.25" customWidth="1"/>
-    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.19921875" customWidth="1"/>
+    <col min="3" max="3" width="9.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -1305,7 +1308,7 @@
         <v>156790</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -1316,7 +1319,7 @@
         <v>36400</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1327,7 +1330,7 @@
         <v>267600</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -1338,7 +1341,7 @@
         <v>24400</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1358,12 +1361,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>32</v>
       </c>
